--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92566148777</v>
+        <v>46157.93091903713</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93091903713</v>
+        <v>46157.93168971785</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93168971785</v>
+        <v>46157.93398067219</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93398067219</v>
+        <v>46157.93715806647</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93715806647</v>
+        <v>46158.28214437109</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28214437109</v>
+        <v>46158.29675849281</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29675849281</v>
+        <v>46158.29812520299</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29812520299</v>
+        <v>46158.33385402655</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33385402655</v>
+        <v>46158.36855161248</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36855161248</v>
+        <v>46158.37285922524</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
